--- a/data/daschland_ontology/json_header.xlsx
+++ b/data/daschland_ontology/json_header.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noraammann/Documents/Cloned_GitHub/daschland-scripts/daschland_ontology/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noraammann/Documents/Cloned_GitHub/0854-daschland-scripts/data/daschland_ontology/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19753C7-EEBC-4E44-82F8-4B804657A967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86462C40-0B07-1F4C-BAE5-F10F2224DA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44620" yWindow="620" windowWidth="32180" windowHeight="30260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20460" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prefixes" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Keywords" sheetId="4" r:id="rId4"/>
     <sheet name="Users" sheetId="5" r:id="rId5"/>
     <sheet name="Licenses" sheetId="6" r:id="rId6"/>
+    <sheet name="data legal settings" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="88">
   <si>
     <t>username</t>
   </si>
@@ -302,12 +302,27 @@
   <si>
     <t>http://rdfh.ch/licenses/cc-0-1.0</t>
   </si>
+  <si>
+    <t>data_license</t>
+  </si>
+  <si>
+    <t>data_copyright_holder</t>
+  </si>
+  <si>
+    <t>default_data_authorship</t>
+  </si>
+  <si>
+    <t>Alice Liddell</t>
+  </si>
+  <si>
+    <t>Caterpillar Wonderland</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,6 +397,14 @@
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -411,7 +434,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -462,6 +485,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -16290,4 +16314,46 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2D9521-9263-7F47-90D6-70FDCF93FFD0}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>